--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104634_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104634_W20.xlsx
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.9599</v>
+        <v>3.7462</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0553</v>
+        <v>3.2804</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9046999999999999</v>
+        <v>0.4659</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.957</v>
+        <v>-0.9516</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.0721</v>
+        <v>-0.0745</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.8849</v>
+        <v>-0.877</v>
       </c>
       <c r="J2" t="n">
-        <v>1.185</v>
+        <v>1.1677</v>
       </c>
       <c r="K2" t="n">
-        <v>0.4014</v>
+        <v>0.3857</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7837</v>
+        <v>0.782</v>
       </c>
       <c r="M2" t="n">
-        <v>-2.142</v>
+        <v>-2.1193</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.4735</v>
+        <v>-0.4603</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.6685</v>
+        <v>-1.659</v>
       </c>
       <c r="P2" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S2" t="n">
-        <v>5.5725</v>
+        <v>2.3515</v>
       </c>
       <c r="T2" t="n">
-        <v>4.7756</v>
+        <v>2.0248</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7969000000000001</v>
+        <v>0.3267</v>
       </c>
       <c r="V2" t="n">
-        <v>0.9834000000000001</v>
+        <v>0.9805</v>
       </c>
       <c r="W2" t="n">
-        <v>0.3214</v>
+        <v>0.3155</v>
       </c>
       <c r="X2" t="n">
-        <v>0.662</v>
+        <v>0.665</v>
       </c>
     </row>
     <row r="3">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.9803</v>
+        <v>0.9412</v>
       </c>
       <c r="E3" t="n">
-        <v>2.6601</v>
+        <v>1.8245</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6798</v>
+        <v>-0.8833</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.3904</v>
+        <v>-0.3861</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.505</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1147</v>
+        <v>0.1194</v>
       </c>
       <c r="J3" t="n">
-        <v>1.2563</v>
+        <v>1.2465</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0622</v>
+        <v>0.055</v>
       </c>
       <c r="L3" t="n">
-        <v>1.1941</v>
+        <v>1.1916</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.6467</v>
+        <v>-1.6326</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.5672</v>
+        <v>-0.5604</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.0795</v>
+        <v>-1.0722</v>
       </c>
       <c r="P3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>0.849</v>
+        <v>-0.1963</v>
       </c>
       <c r="T3" t="n">
-        <v>1.2431</v>
+        <v>0.4202</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3941</v>
+        <v>-0.6165</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5586</v>
+        <v>0.8776</v>
       </c>
       <c r="E4" t="n">
-        <v>1.2016</v>
+        <v>1.6576</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.643</v>
+        <v>-0.78</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.5325</v>
+        <v>-0.5266</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2655</v>
+        <v>-1.2611</v>
       </c>
       <c r="I4" t="n">
-        <v>0.733</v>
+        <v>0.7344000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.8046</v>
+        <v>0.7914</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.163</v>
+        <v>-0.1691</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9675</v>
+        <v>0.9605</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.3371</v>
+        <v>-1.318</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.1026</v>
+        <v>-1.092</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.2345</v>
+        <v>-0.226</v>
       </c>
       <c r="P4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3625</v>
+        <v>-1.051</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.6956</v>
+        <v>-0.2232</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.6669</v>
+        <v>-0.8278</v>
       </c>
       <c r="V4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0538</v>
+        <v>-0.0097</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0032</v>
+        <v>0.1387</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.0571</v>
+        <v>-0.1484</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.5565</v>
+        <v>-4.568</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.3707</v>
+        <v>-2.375</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1858</v>
+        <v>-2.193</v>
       </c>
       <c r="J5" t="n">
-        <v>-2.3936</v>
+        <v>-2.4331</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.1886</v>
+        <v>-1.2108</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.205</v>
+        <v>-1.2223</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.1629</v>
+        <v>-2.135</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1821</v>
+        <v>-1.1642</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9808</v>
+        <v>-0.9708</v>
       </c>
       <c r="P5" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>0.8783</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="T5" t="n">
-        <v>0.7047</v>
+        <v>0.8983</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1736</v>
+        <v>0.0468</v>
       </c>
       <c r="V5" t="n">
-        <v>2.9438</v>
+        <v>2.9303</v>
       </c>
       <c r="W5" t="n">
-        <v>3.0531</v>
+        <v>3.0392</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. DIAGNE</t>
+          <t>G. GOLOMAN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.098</v>
+        <v>-0.3569</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8774</v>
+        <v>0.6112</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.9754</v>
+        <v>-0.9681</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.9724</v>
+        <v>-0.5018</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.8471</v>
+        <v>0.198</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.1253</v>
+        <v>-0.6998</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1839</v>
+        <v>0.5861</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0346</v>
+        <v>0.5861</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1493</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1563</v>
+        <v>-1.0879</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8817</v>
+        <v>-0.3881</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2745</v>
+        <v>-0.6998</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.6805</v>
+        <v>0.9105</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S6" t="n">
-        <v>0.4621</v>
+        <v>-0.9233</v>
       </c>
       <c r="T6" t="n">
-        <v>0.7349</v>
+        <v>-0.1326</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2728</v>
+        <v>-0.7907</v>
       </c>
       <c r="V6" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. GOLOMAN</t>
+          <t>A. DIAGNE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.8115</v>
+        <v>-0.5039</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2626</v>
+        <v>0.3994</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.074</v>
+        <v>-0.9033</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5116000000000001</v>
+        <v>-0.9638</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1947</v>
+        <v>-0.8418</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7063</v>
+        <v>-0.122</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5888</v>
+        <v>0.1834</v>
       </c>
       <c r="K7" t="n">
-        <v>0.5888</v>
+        <v>0.0345</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.1489</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1003</v>
+        <v>-1.1472</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.394</v>
+        <v>-0.8763</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.7063</v>
+        <v>-0.271</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.368</v>
+        <v>0.0534</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.4869</v>
+        <v>0.2647</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.881</v>
+        <v>-0.2113</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="W7" t="n">
-        <v>0.1607</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.8154</v>
+        <v>-1.124</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6766</v>
+        <v>0.1739</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1388</v>
+        <v>-1.2979</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.1092</v>
+        <v>-1.1264</v>
       </c>
       <c r="H8" t="n">
-        <v>-1.8901</v>
+        <v>-1.9007</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7809</v>
+        <v>0.7743</v>
       </c>
       <c r="J8" t="n">
-        <v>1.1584</v>
+        <v>1.1219</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.4484</v>
+        <v>-1.4694</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6068</v>
+        <v>2.5912</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.2675</v>
+        <v>-2.2483</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.4417</v>
+        <v>-0.4314</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.8258</v>
+        <v>-1.8169</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.4952</v>
+        <v>-2.5039</v>
       </c>
       <c r="R8" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1434</v>
+        <v>0.5666</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4325</v>
+        <v>0.4665</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2891</v>
+        <v>0.1002</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.1093</v>
+        <v>-0.1089</v>
       </c>
       <c r="W8" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2019</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. SANZ</t>
+          <t>J. BATEMON</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7234</v>
+        <v>-2.132</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0965</v>
+        <v>0.1631</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.6269</v>
+        <v>-2.2951</v>
       </c>
       <c r="G9" t="n">
-        <v>-4.6443</v>
+        <v>-3.3978</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.896</v>
+        <v>-1.8122</v>
       </c>
       <c r="I9" t="n">
-        <v>-2.7482</v>
+        <v>-1.5856</v>
       </c>
       <c r="J9" t="n">
-        <v>-2.2814</v>
+        <v>-0.3615</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.8871</v>
+        <v>-1.1796</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3942</v>
+        <v>0.8181</v>
       </c>
       <c r="M9" t="n">
-        <v>-2.3629</v>
+        <v>-3.0364</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.0089</v>
+        <v>-0.6326000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.354</v>
+        <v>-2.4037</v>
       </c>
       <c r="P9" t="n">
-        <v>1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.2268</v>
+        <v>-1.3658</v>
       </c>
       <c r="R9" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0094</v>
+        <v>0.6919</v>
       </c>
       <c r="T9" t="n">
-        <v>0.7047</v>
+        <v>0.8008999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7141</v>
+        <v>-0.1089</v>
       </c>
       <c r="V9" t="n">
-        <v>0.1156</v>
+        <v>-0.1089</v>
       </c>
       <c r="W9" t="n">
-        <v>0.7071</v>
+        <v>1.0895</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5914</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. BATEMON</t>
+          <t>M. SANZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.8018</v>
+        <v>-2.1877</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.1594</v>
+        <v>-0.9467</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.6424</v>
+        <v>-1.241</v>
       </c>
       <c r="G10" t="n">
-        <v>-3.381</v>
+        <v>-4.6549</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.8109</v>
+        <v>-1.8956</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5701</v>
+        <v>-2.7593</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.3195</v>
+        <v>-2.3199</v>
       </c>
       <c r="K10" t="n">
-        <v>-1.1642</v>
+        <v>-0.9038</v>
       </c>
       <c r="L10" t="n">
-        <v>0.8448</v>
+        <v>-1.4161</v>
       </c>
       <c r="M10" t="n">
-        <v>-3.0615</v>
+        <v>-2.335</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.6467000000000001</v>
+        <v>-0.9918</v>
       </c>
       <c r="O10" t="n">
-        <v>-2.4149</v>
+        <v>-1.3432</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6805</v>
+        <v>1.8211</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.992</v>
+        <v>0.5258</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5716</v>
+        <v>0.8983</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4204</v>
+        <v>-0.3725</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.1093</v>
+        <v>0.1203</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0927</v>
+        <v>0.7025</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.2019</v>
+        <v>-0.5822000000000001</v>
       </c>
     </row>
     <row r="11">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.3245</v>
+        <v>-3.777</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.3287</v>
+        <v>-0.9974</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.9957</v>
+        <v>-2.7795</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.4115</v>
+        <v>-3.412</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.6694</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.7375</v>
+        <v>-2.7426</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2804</v>
+        <v>-1.306</v>
       </c>
       <c r="K11" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.6238</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.914</v>
+        <v>-1.9298</v>
       </c>
       <c r="M11" t="n">
-        <v>-2.1311</v>
+        <v>-2.1061</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.3075</v>
+        <v>-1.2932</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.1813</v>
+        <v>-0.6412</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0484</v>
+        <v>0.3085</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.133</v>
+        <v>-0.9498</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.759</v>
+        <v>-6.0115</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.2452</v>
+        <v>-3.6797</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.5137</v>
+        <v>-2.3318</v>
       </c>
       <c r="G12" t="n">
-        <v>-5.2671</v>
+        <v>-5.2706</v>
       </c>
       <c r="H12" t="n">
-        <v>-1.1355</v>
+        <v>-1.14</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.1316</v>
+        <v>-4.1307</v>
       </c>
       <c r="J12" t="n">
-        <v>-2.6423</v>
+        <v>-2.6644</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.3952</v>
+        <v>-0.4072</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2471</v>
+        <v>-2.2572</v>
       </c>
       <c r="M12" t="n">
-        <v>-2.6248</v>
+        <v>-2.6062</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.7328</v>
       </c>
       <c r="O12" t="n">
-        <v>-1.8844</v>
+        <v>-1.8734</v>
       </c>
       <c r="P12" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R12" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.4653</v>
+        <v>-0.7213000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4688</v>
+        <v>0.1228</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.9966</v>
+        <v>-0.8441</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.8886</v>
+        <v>-10.5377</v>
       </c>
       <c r="E13" t="n">
-        <v>2.5538</v>
+        <v>2.625000000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-13.4421</v>
+        <v>-13.1625</v>
       </c>
       <c r="G13" t="n">
-        <v>-25.7335</v>
+        <v>-25.7596</v>
       </c>
       <c r="H13" t="n">
-        <v>-12.2721</v>
+        <v>-12.2778</v>
       </c>
       <c r="I13" t="n">
-        <v>-13.4611</v>
+        <v>-13.4819</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7402</v>
+        <v>-3.9879</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.5259</v>
+        <v>-3.6548</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2141000000000006</v>
+        <v>-0.3331000000000006</v>
       </c>
       <c r="M13" t="n">
-        <v>-21.9931</v>
+        <v>-21.772</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.7463</v>
+        <v>-8.623099999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>-13.2468</v>
+        <v>-13.1489</v>
       </c>
       <c r="P13" t="n">
-        <v>9.073300000000001</v>
+        <v>9.1053</v>
       </c>
       <c r="Q13" t="n">
-        <v>-7.9392</v>
+        <v>-7.9671</v>
       </c>
       <c r="R13" t="n">
-        <v>17.0125</v>
+        <v>17.0725</v>
       </c>
       <c r="S13" t="n">
-        <v>1.239999999999999</v>
+        <v>1.6012</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4592</v>
+        <v>5.8492</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.2193</v>
+        <v>-4.2479</v>
       </c>
       <c r="V13" t="n">
-        <v>4.531200000000001</v>
+        <v>4.5159</v>
       </c>
       <c r="W13" t="n">
-        <v>8.773800000000001</v>
+        <v>8.7308</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.242299999999999</v>
+        <v>-4.214899999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.0827</v>
+        <v>5.8681</v>
       </c>
       <c r="E14" t="n">
-        <v>4.4206</v>
+        <v>4.8652</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6621</v>
+        <v>1.0029</v>
       </c>
       <c r="G14" t="n">
-        <v>5.8614</v>
+        <v>5.8644</v>
       </c>
       <c r="H14" t="n">
-        <v>1.2741</v>
+        <v>1.2779</v>
       </c>
       <c r="I14" t="n">
-        <v>4.5874</v>
+        <v>4.5865</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4904</v>
+        <v>4.4715</v>
       </c>
       <c r="K14" t="n">
-        <v>1.7317</v>
+        <v>1.7237</v>
       </c>
       <c r="L14" t="n">
-        <v>2.7587</v>
+        <v>2.7479</v>
       </c>
       <c r="M14" t="n">
-        <v>1.371</v>
+        <v>1.3928</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4576</v>
+        <v>-0.4458</v>
       </c>
       <c r="O14" t="n">
-        <v>1.8286</v>
+        <v>1.8386</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.4537</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.2249</v>
+        <v>-0.4411</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.3478</v>
+        <v>0.1253</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.8771</v>
+        <v>-0.5664</v>
       </c>
       <c r="V14" t="n">
-        <v>0.8998</v>
+        <v>0.9002</v>
       </c>
       <c r="W14" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="X14" t="n">
-        <v>-0.7392</v>
+        <v>-0.7341</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.4243</v>
+        <v>4.1676</v>
       </c>
       <c r="E15" t="n">
-        <v>3.7071</v>
+        <v>3.456</v>
       </c>
       <c r="F15" t="n">
-        <v>0.7171999999999999</v>
+        <v>0.7117</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2468</v>
+        <v>5.2499</v>
       </c>
       <c r="H15" t="n">
-        <v>1.8989</v>
+        <v>1.9012</v>
       </c>
       <c r="I15" t="n">
-        <v>3.3479</v>
+        <v>3.3487</v>
       </c>
       <c r="J15" t="n">
-        <v>3.3563</v>
+        <v>3.34</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6797</v>
+        <v>1.672</v>
       </c>
       <c r="L15" t="n">
-        <v>1.6765</v>
+        <v>1.668</v>
       </c>
       <c r="M15" t="n">
-        <v>1.8905</v>
+        <v>1.9099</v>
       </c>
       <c r="N15" t="n">
-        <v>0.2192</v>
+        <v>0.2292</v>
       </c>
       <c r="O15" t="n">
-        <v>1.6714</v>
+        <v>1.6807</v>
       </c>
       <c r="P15" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S15" t="n">
-        <v>0.0094</v>
+        <v>-0.2587</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5777</v>
+        <v>0.3436</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.5683</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="V15" t="n">
-        <v>-1.2855</v>
+        <v>-1.2788</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2855</v>
+        <v>-1.2788</v>
       </c>
     </row>
     <row r="16">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.9163</v>
+        <v>2.8927</v>
       </c>
       <c r="E16" t="n">
-        <v>2.055</v>
+        <v>1.1986</v>
       </c>
       <c r="F16" t="n">
-        <v>1.8613</v>
+        <v>1.6941</v>
       </c>
       <c r="G16" t="n">
-        <v>3.1095</v>
+        <v>3.107</v>
       </c>
       <c r="H16" t="n">
-        <v>2.0059</v>
+        <v>1.9939</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1036</v>
+        <v>1.1132</v>
       </c>
       <c r="J16" t="n">
-        <v>2.1494</v>
+        <v>2.1274</v>
       </c>
       <c r="K16" t="n">
-        <v>1.4404</v>
+        <v>1.4199</v>
       </c>
       <c r="L16" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9601</v>
+        <v>0.9796</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5655</v>
+        <v>0.574</v>
       </c>
       <c r="O16" t="n">
-        <v>0.3946</v>
+        <v>0.4057</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.0415</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S16" t="n">
-        <v>2.9446</v>
+        <v>1.9373</v>
       </c>
       <c r="T16" t="n">
-        <v>2.2381</v>
+        <v>1.4189</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7065</v>
+        <v>0.5184</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.0963</v>
+        <v>-0.103</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.06419999999999999</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. MARTINEZ</t>
+          <t>M. FJELLERUP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4001</v>
+        <v>1.4866</v>
       </c>
       <c r="E17" t="n">
-        <v>3.5454</v>
+        <v>0.9046</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.1453</v>
+        <v>0.582</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8891</v>
+        <v>2.9879</v>
       </c>
       <c r="H17" t="n">
-        <v>2.1311</v>
+        <v>1.5024</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.242</v>
+        <v>1.4855</v>
       </c>
       <c r="J17" t="n">
-        <v>1.8902</v>
+        <v>2.1242</v>
       </c>
       <c r="K17" t="n">
-        <v>1.8183</v>
+        <v>1.4167</v>
       </c>
       <c r="L17" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.7075</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.0011</v>
+        <v>0.8638</v>
       </c>
       <c r="N17" t="n">
-        <v>0.3129</v>
+        <v>0.0857</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.314</v>
+        <v>0.778</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.2268</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1342</v>
+        <v>-1.3658</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S17" t="n">
-        <v>2.8306</v>
+        <v>-0.2437</v>
       </c>
       <c r="T17" t="n">
-        <v>2.468</v>
+        <v>0.1462</v>
       </c>
       <c r="U17" t="n">
-        <v>0.3626</v>
+        <v>-0.3899</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.0927</v>
+        <v>-0.3471</v>
       </c>
       <c r="W17" t="n">
-        <v>0.3214</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.4141</v>
+        <v>-0.3471</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. FJELLERUP</t>
+          <t>P. BUSQUETS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6883</v>
+        <v>1.4692</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5695</v>
+        <v>1.955</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1187</v>
+        <v>-0.4858</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9848</v>
+        <v>4.4843</v>
       </c>
       <c r="H18" t="n">
-        <v>1.508</v>
+        <v>2.0447</v>
       </c>
       <c r="I18" t="n">
-        <v>1.4768</v>
+        <v>2.4397</v>
       </c>
       <c r="J18" t="n">
-        <v>2.1392</v>
+        <v>4.2203</v>
       </c>
       <c r="K18" t="n">
-        <v>1.4302</v>
+        <v>1.2271</v>
       </c>
       <c r="L18" t="n">
-        <v>0.709</v>
+        <v>2.9932</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8455</v>
+        <v>0.2641</v>
       </c>
       <c r="N18" t="n">
-        <v>0.07779999999999999</v>
+        <v>0.8176</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7678</v>
+        <v>-0.5535</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.9073</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.361</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>0.4537</v>
+        <v>1.1382</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0356</v>
+        <v>-0.1729</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2087</v>
+        <v>0.0809</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8269</v>
+        <v>-0.2538</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.3536</v>
+        <v>-1.4764</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3536</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>P. BUSQUETS</t>
+          <t>S. MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.462</v>
+        <v>0.8857</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1728</v>
+        <v>2.1128</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7108</v>
+        <v>-1.2271</v>
       </c>
       <c r="G19" t="n">
-        <v>4.4872</v>
+        <v>0.9078000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>2.0403</v>
+        <v>2.1393</v>
       </c>
       <c r="I19" t="n">
-        <v>2.4469</v>
+        <v>-1.2314</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2542</v>
+        <v>1.8767</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2397</v>
+        <v>1.8099</v>
       </c>
       <c r="L19" t="n">
-        <v>3.0145</v>
+        <v>0.0668</v>
       </c>
       <c r="M19" t="n">
-        <v>0.2329</v>
+        <v>-0.9689</v>
       </c>
       <c r="N19" t="n">
-        <v>0.8006</v>
+        <v>0.3294</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5676</v>
+        <v>-1.2982</v>
       </c>
       <c r="P19" t="n">
-        <v>-1.361</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.4952</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.1859</v>
+        <v>1.295</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.747</v>
+        <v>1.0587</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.4389</v>
+        <v>0.2363</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.4783</v>
+        <v>-1.0895</v>
       </c>
       <c r="W19" t="n">
-        <v>0.1607</v>
+        <v>0.3155</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.639</v>
+        <v>-1.405</v>
       </c>
     </row>
     <row r="20">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8273</v>
+        <v>-0.5947</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.424</v>
+        <v>-1.8051</v>
       </c>
       <c r="F20" t="n">
-        <v>0.5967</v>
+        <v>1.2104</v>
       </c>
       <c r="G20" t="n">
-        <v>2.2342</v>
+        <v>2.2414</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.6739000000000001</v>
+        <v>-0.6694</v>
       </c>
       <c r="I20" t="n">
-        <v>2.9081</v>
+        <v>2.9108</v>
       </c>
       <c r="J20" t="n">
-        <v>0.6741</v>
+        <v>0.6618000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4054</v>
+        <v>-0.4104</v>
       </c>
       <c r="L20" t="n">
-        <v>1.0795</v>
+        <v>1.0722</v>
       </c>
       <c r="M20" t="n">
-        <v>1.5601</v>
+        <v>1.5796</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2685</v>
+        <v>-0.259</v>
       </c>
       <c r="O20" t="n">
-        <v>1.8286</v>
+        <v>1.8386</v>
       </c>
       <c r="P20" t="n">
-        <v>-3.1757</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.6293</v>
+        <v>-3.6421</v>
       </c>
       <c r="R20" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.9463</v>
+        <v>-0.7071</v>
       </c>
       <c r="T20" t="n">
-        <v>0.4386</v>
+        <v>0.0858</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.3849</v>
+        <v>-0.7929</v>
       </c>
       <c r="V20" t="n">
-        <v>1.0605</v>
+        <v>1.0579</v>
       </c>
       <c r="W20" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.0321</v>
+        <v>-0.0316</v>
       </c>
     </row>
     <row r="21">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9459</v>
+        <v>-0.7358</v>
       </c>
       <c r="E21" t="n">
-        <v>1.7971</v>
+        <v>1.5315</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.7431</v>
+        <v>-2.2673</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.0493</v>
+        <v>-0.0539</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9076</v>
+        <v>-0.9103</v>
       </c>
       <c r="I21" t="n">
-        <v>0.8583</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7628</v>
+        <v>0.7282</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.8813</v>
+        <v>-1.9003</v>
       </c>
       <c r="L21" t="n">
-        <v>2.6441</v>
+        <v>2.6285</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.8121</v>
+        <v>-0.7821</v>
       </c>
       <c r="N21" t="n">
-        <v>0.9737</v>
+        <v>0.99</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q21" t="n">
         <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3814</v>
+        <v>0.5865</v>
       </c>
       <c r="T21" t="n">
-        <v>1.0344</v>
+        <v>0.8033</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.653</v>
+        <v>-0.2168</v>
       </c>
       <c r="V21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.1853</v>
+        <v>-2.1789</v>
       </c>
     </row>
     <row r="22">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.547</v>
+        <v>-0.9406</v>
       </c>
       <c r="E22" t="n">
-        <v>0.0535</v>
+        <v>0.3794</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6005</v>
+        <v>-1.32</v>
       </c>
       <c r="G22" t="n">
-        <v>0.2958</v>
+        <v>0.3007</v>
       </c>
       <c r="H22" t="n">
-        <v>1.2741</v>
+        <v>1.2779</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.9782</v>
+        <v>-0.9771</v>
       </c>
       <c r="J22" t="n">
-        <v>0.7906</v>
+        <v>0.7698</v>
       </c>
       <c r="K22" t="n">
-        <v>0.9453</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.1547</v>
+        <v>-0.1643</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4948</v>
+        <v>-0.469</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3288</v>
+        <v>0.3438</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.8236</v>
+        <v>-0.8129</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.8428</v>
+        <v>-1.2414</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.6956</v>
+        <v>-0.3417</v>
       </c>
       <c r="U22" t="n">
-        <v>-1.1472</v>
+        <v>-0.8997000000000001</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="23">
@@ -2203,58 +2203,58 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.7649</v>
+        <v>-1.2438</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4549</v>
+        <v>-1.4354</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.31</v>
+        <v>0.1916</v>
       </c>
       <c r="G23" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.6701</v>
       </c>
       <c r="H23" t="n">
-        <v>1.7215</v>
+        <v>1.7204</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.0476</v>
+        <v>-1.0503</v>
       </c>
       <c r="J23" t="n">
-        <v>1.4859</v>
+        <v>1.4522</v>
       </c>
       <c r="K23" t="n">
-        <v>0.7477</v>
+        <v>0.7305</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7382</v>
+        <v>0.7217</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8121</v>
+        <v>-0.7821</v>
       </c>
       <c r="N23" t="n">
-        <v>0.9737</v>
+        <v>0.99</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.7858</v>
+        <v>-1.772</v>
       </c>
       <c r="P23" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="Q23" t="n">
-        <v>-3.4025</v>
+        <v>-3.4145</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1342</v>
+        <v>1.1382</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1705</v>
+        <v>0.3624</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.5383</v>
+        <v>0.5269</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6321</v>
+        <v>-0.1645</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>10.8886</v>
+        <v>13.255</v>
       </c>
       <c r="E24" t="n">
-        <v>13.4421</v>
+        <v>13.1626</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.5537</v>
+        <v>0.0924999999999998</v>
       </c>
       <c r="G24" t="n">
-        <v>25.7334</v>
+        <v>25.7596</v>
       </c>
       <c r="H24" t="n">
-        <v>12.2724</v>
+        <v>12.278</v>
       </c>
       <c r="I24" t="n">
-        <v>13.4612</v>
+        <v>13.482</v>
       </c>
       <c r="J24" t="n">
-        <v>21.9931</v>
+        <v>21.7721</v>
       </c>
       <c r="K24" t="n">
-        <v>8.7463</v>
+        <v>8.623099999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>13.2467</v>
+        <v>13.149</v>
       </c>
       <c r="M24" t="n">
-        <v>3.739999999999999</v>
+        <v>3.987699999999999</v>
       </c>
       <c r="N24" t="n">
-        <v>3.5261</v>
+        <v>3.6549</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2141999999999999</v>
+        <v>0.3330000000000004</v>
       </c>
       <c r="P24" t="n">
-        <v>-9.0733</v>
+        <v>-9.1052</v>
       </c>
       <c r="Q24" t="n">
-        <v>-17.0125</v>
+        <v>-17.0724</v>
       </c>
       <c r="R24" t="n">
-        <v>7.9392</v>
+        <v>7.967200000000001</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.24</v>
+        <v>1.1163</v>
       </c>
       <c r="T24" t="n">
-        <v>4.2194</v>
+        <v>4.2479</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.459300000000001</v>
+        <v>-3.1316</v>
       </c>
       <c r="V24" t="n">
-        <v>-4.5314</v>
+        <v>-4.5156</v>
       </c>
       <c r="W24" t="n">
-        <v>4.2423</v>
+        <v>4.215100000000001</v>
       </c>
       <c r="X24" t="n">
-        <v>-8.7736</v>
+        <v>-8.7308</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104634_W20.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104634_W20.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0.665</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-0.5822000000000001</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.214899999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-0.7341</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-1.2788</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.0316</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3471</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-1.405</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.0316</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-2.1789</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104634_W20.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,7 @@
       <c r="X24" t="n">
         <v>-8.7308</v>
       </c>
+      <c r="Y24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
